--- a/out/MLP-Mamba1_repeat_1_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9612393007297437</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9612393007297437</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.561239300729744</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.854026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.854026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.854026995542006</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.854026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.9817726438401608</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.254026995542006</v>
+        <v>1.829132276861947</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.254026995542006</v>
+        <v>-1.581772643840161</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.561239300729744</v>
+        <v>1.229132276861947</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_1_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.254026995542006</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685294</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9612393007297437</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.854026995542006</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9612393007297437</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.7048498062146814</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.9048498062146815</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.06136036706685299</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.854026995542006</v>
+        <v>0.5821290720809755</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.254026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA91" t="n">
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.561239300729744</v>
+        <v>-0.2613603670668529</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.854026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.254026995542006</v>
+        <v>1.225618511228804</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.254026995542006</v>
+        <v>1.025618511228804</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.254026995542006</v>
+        <v>0.3821290720809755</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.561239300729744</v>
+        <v>0.06038435250706121</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_1_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.4710423052310944</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4827371835708618</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.501964807510376</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.4774428606033325</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4432043135166168</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.4662362337112427</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4989167153835297</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4064829051494598</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4220872223377228</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4034836888313293</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4465740621089935</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4066762328147888</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.4213398993015289</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4096063077449799</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4142068326473236</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.16</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5235483050346375</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.06136036706685294</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4915002584457397</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5643513798713684</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4660175740718842</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.5479744672775269</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.4554222226142883</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.16</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3959378600120544</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3882759809494019</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>0.479617178440094</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4188952147960663</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3915634453296661</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4669999480247498</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3951514959335327</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4091062843799591</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4425096809864044</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.06136036706685299</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.5844670534133911</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.451390266418457</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.3946439921855927</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.7048498062146814</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.4371612071990967</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.7048498062146814</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3814539611339569</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.370972216129303</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4592999219894409</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4270925223827362</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.3831746578216553</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4462155997753143</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.4186184108257294</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>0.4016726613044739</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>0.384322315454483</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.3883562386035919</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.424826979637146</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.3908917009830475</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.4132183194160461</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3850899338722229</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.3891270756721497</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.4029371440410614</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4554109573364258</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4191061854362488</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.3</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.3830569088459015</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.4530802667140961</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.3</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3715678751468658</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.5206896662712097</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.383830338716507</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.4505918025970459</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.7048498062146814</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4361025094985962</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.7048498062146814</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.3665988743305206</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3840298354625702</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3801532387733459</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3880796134471893</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3833032548427582</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.3792376518249512</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4190197288990021</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3819836676120758</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.374570369720459</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9048498062146815</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.4002977609634399</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3660080432891846</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.3032301962375641</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9048498062146815</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.3524111807346344</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.06136036706685299</v>
+        <v>0.16</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.59375</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.5821290720809755</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.5136986970901489</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.6200666427612305</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.225618511228804</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.5992593765258789</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.225618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5877407789230347</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.225618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.5202063918113708</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5227441787719727</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5545240640640259</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.5164591670036316</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.225618511228804</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6457725763320923</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.225618511228804</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.5594019889831543</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.025618511228804</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.6283891201019287</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.025618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.5440278053283691</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.025618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.587212085723877</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.025618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.6097006797790527</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.6090090274810791</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4801073372364044</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4859926402568817</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.2613603670668529</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.556785523891449</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.5231366753578186</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.6010522842407227</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.225618511228804</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.5797293186187744</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.225618511228804</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6531667113304138</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.5306797623634338</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.225618511228804</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.5446779131889343</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.225618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.5702760815620422</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.225618511228804</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.5482304096221924</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.225618511228804</v>
+        <v>-0.16</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.5250409841537476</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.225618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.6811603307723999</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.3</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.5628693699836731</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.590122401714325</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.6214863061904907</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.025618511228804</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.5649023652076721</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.025618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.574870228767395</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.025618511228804</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.5704934597015381</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.025618511228804</v>
+        <v>0.3</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5693152546882629</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.6037555932998657</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.5314699411392212</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.3</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.5719162821769714</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.16</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.5884161591529846</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.025618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.8003314137458801</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.025618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.6769541501998901</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.025618511228804</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.8790542483329773</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.025618511228804</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.7802602648735046</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.025618511228804</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.7981600761413574</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.025618511228804</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.7429841756820679</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.5943448543548584</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.5905302166938782</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.7378851175308228</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.73114413022995</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.7962067127227783</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.025618511228804</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.5109681487083435</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.3821290720809755</v>
+        <v>-0.6500000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4614363312721252</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.06038435250706121</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-Mamba1_repeat_1_000005.xlsx
+++ b/out/MLP-Mamba1_repeat_1_000005.xlsx
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.4432043135166168</v>
+        <v>0.4432043731212616</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.7199999999999999</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.4213398993015289</v>
+        <v>0.4213398694992065</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.4142068326473236</v>
+        <v>0.4142068922519684</v>
       </c>
       <c r="JB16" t="n">
         <v>0.16</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4091062843799591</v>
+        <v>0.4091063141822815</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.3946439921855927</v>
+        <v>0.3946439623832703</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.5799999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.4132183194160461</v>
+        <v>0.4132182896137238</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.3891270756721497</v>
+        <v>0.3891271352767944</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.1199999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3801532387733459</v>
+        <v>0.3801532089710236</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.4190197288990021</v>
+        <v>0.4190196692943573</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.59375</v>
+        <v>0.5937499403953552</v>
       </c>
       <c r="JB74" t="n">
         <v>0.4399999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.5136986970901489</v>
+        <v>0.5136987566947937</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.587212085723877</v>
+        <v>0.5872120261192322</v>
       </c>
       <c r="JB87" t="n">
         <v>0.7199999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.556785523891449</v>
+        <v>0.5567854642868042</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.5231366753578186</v>
+        <v>0.5231366157531738</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.6010522842407227</v>
+        <v>0.6010522246360779</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.02000000000000007</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.5446779131889343</v>
+        <v>0.5446778535842896</v>
       </c>
       <c r="JB98" t="n">
         <v>0.5799999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.5628693699836731</v>
+        <v>0.5628693103790283</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1600000000000001</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.6037555932998657</v>
+        <v>0.6037556529045105</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.4399999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.5314699411392212</v>
+        <v>0.5314698815345764</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.3</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.8003314137458801</v>
+        <v>0.8003313541412354</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.6769541501998901</v>
+        <v>0.6769542098045349</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.7429841756820679</v>
+        <v>0.7429841160774231</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.3</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.7378851175308228</v>
+        <v>0.737885057926178</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
